--- a/artfynd/A 19334-2025 artfynd.xlsx
+++ b/artfynd/A 19334-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74723793</v>
       </c>
       <c r="B2" t="n">
-        <v>97952</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100251</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592617.7514560737</v>
+        <v>592618</v>
       </c>
       <c r="R2" t="n">
-        <v>6354449.401312793</v>
+        <v>6354449</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1983-08-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1983-08-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -799,12 +784,7 @@
         <v>75143818</v>
       </c>
       <c r="B3" t="n">
-        <v>104404</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106902</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592517.0318956285</v>
+        <v>592517</v>
       </c>
       <c r="R3" t="n">
-        <v>6354548.122971674</v>
+        <v>6354548</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -869,19 +849,9 @@
           <t>1989-06-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1989-06-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 19334-2025 artfynd.xlsx
+++ b/artfynd/A 19334-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74723793</v>
       </c>
       <c r="B2" t="n">
-        <v>100251</v>
+        <v>100257</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>75143818</v>
       </c>
       <c r="B3" t="n">
-        <v>106902</v>
+        <v>106911</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19334-2025 artfynd.xlsx
+++ b/artfynd/A 19334-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74723793</v>
       </c>
       <c r="B2" t="n">
-        <v>100257</v>
+        <v>100258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>75143818</v>
       </c>
       <c r="B3" t="n">
-        <v>106911</v>
+        <v>106916</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19334-2025 artfynd.xlsx
+++ b/artfynd/A 19334-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74723793</v>
       </c>
       <c r="B2" t="n">
-        <v>100258</v>
+        <v>100285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>75143818</v>
       </c>
       <c r="B3" t="n">
-        <v>106916</v>
+        <v>106944</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19334-2025 artfynd.xlsx
+++ b/artfynd/A 19334-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74723793</v>
       </c>
       <c r="B2" t="n">
-        <v>100285</v>
+        <v>100291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>75143818</v>
       </c>
       <c r="B3" t="n">
-        <v>106944</v>
+        <v>106950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19334-2025 artfynd.xlsx
+++ b/artfynd/A 19334-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74723793</v>
       </c>
       <c r="B2" t="n">
-        <v>100291</v>
+        <v>100298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>75143818</v>
       </c>
       <c r="B3" t="n">
-        <v>106950</v>
+        <v>106957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19334-2025 artfynd.xlsx
+++ b/artfynd/A 19334-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74723793</v>
       </c>
       <c r="B2" t="n">
-        <v>100298</v>
+        <v>100302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>75143818</v>
       </c>
       <c r="B3" t="n">
-        <v>106957</v>
+        <v>106961</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19334-2025 artfynd.xlsx
+++ b/artfynd/A 19334-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74723793</v>
       </c>
       <c r="B2" t="n">
-        <v>100302</v>
+        <v>100309</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>75143818</v>
       </c>
       <c r="B3" t="n">
-        <v>106961</v>
+        <v>106969</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19334-2025 artfynd.xlsx
+++ b/artfynd/A 19334-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74723793</v>
       </c>
       <c r="B2" t="n">
-        <v>100312</v>
+        <v>100317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>75143818</v>
       </c>
       <c r="B3" t="n">
-        <v>106972</v>
+        <v>106977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19334-2025 artfynd.xlsx
+++ b/artfynd/A 19334-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74723793</v>
       </c>
       <c r="B2" t="n">
-        <v>100317</v>
+        <v>100325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>75143818</v>
       </c>
       <c r="B3" t="n">
-        <v>106977</v>
+        <v>106985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19334-2025 artfynd.xlsx
+++ b/artfynd/A 19334-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74723793</v>
       </c>
       <c r="B2" t="n">
-        <v>100325</v>
+        <v>100335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>75143818</v>
       </c>
       <c r="B3" t="n">
-        <v>106985</v>
+        <v>106995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
